--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -88,21 +88,24 @@
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
     <t>ROCETE</t>
   </si>
   <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -115,13 +118,13 @@
     <t>ALEXIS</t>
   </si>
   <si>
+    <t>MARCO</t>
+  </si>
+  <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
   </si>
   <si>
     <t>ROSA</t>
@@ -1124,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1165,7 +1168,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1179,7 +1182,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920150</v>
+        <v>22330051920097</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1188,13 +1191,13 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1202,22 +1205,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920084</v>
+        <v>22330051920097</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1225,13 +1228,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920126</v>
+        <v>22330051920150</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -1240,7 +1243,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1248,10 +1251,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920070</v>
+        <v>22330051920084</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -1266,6 +1269,29 @@
         <v>13</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920070</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -85,49 +85,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
+    <t>GUERRA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>ROCETE</t>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>ALEXIS</t>
+    <t>CLAUDIA PAOLA</t>
   </si>
   <si>
     <t>MARCO</t>
   </si>
   <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
+    <t>BETSABETH</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
   </si>
   <si>
     <t>ROSA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -749,16 +755,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,16 +804,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.02</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -818,16 +830,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>82.05</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -841,16 +856,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -864,16 +882,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>86.48999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -887,16 +908,19 @@
         <v>42</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>78.56999999999999</v>
+      </c>
+      <c r="H8">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -961,7 +985,7 @@
         <v>94.12</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1004,16 +1028,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>90.7</v>
+        <v>93.02</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1030,16 +1054,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>87.18000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1056,16 +1080,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>87.5</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1082,16 +1106,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>89.19</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1108,16 +1132,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>83.33</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1159,22 +1183,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920321</v>
+        <v>22330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1188,79 +1212,79 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920097</v>
+        <v>22330051920121</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920150</v>
+        <v>22330051920061</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920084</v>
+        <v>22330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1269,21 +1293,21 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920070</v>
+        <v>22330051920317</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -88,9 +88,6 @@
     <t>GUERRA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>TELE</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>RIVERA</t>
   </si>
   <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -119,9 +113,6 @@
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>MARCO</t>
   </si>
   <si>
     <t>BETSABETH</t>
@@ -781,16 +772,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.02</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1011,7 +1005,7 @@
         <v>93.02</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1151,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1189,10 +1183,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1206,19 +1200,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920097</v>
+        <v>22330051920121</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1229,22 +1223,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920121</v>
+        <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1252,16 +1246,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920061</v>
+        <v>22330051920070</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1275,16 +1269,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920070</v>
+        <v>22330051920317</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1293,29 +1287,6 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920317</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
@@ -85,40 +85,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
     <t>TELE</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
     <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
   <si>
     <t>ROSA</t>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920121</v>
+        <v>22330051920212</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1215,15 +1215,15 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920061</v>
+        <v>22330051920121</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1238,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1275,7 +1275,7 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -85,12 +85,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>TELE</t>
   </si>
   <si>
@@ -100,24 +112,51 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
     <t>DANIELA</t>
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>MELISA VIANNEY</t>
+  </si>
+  <si>
     <t>BETSABETH</t>
   </si>
   <si>
@@ -125,6 +164,9 @@
   </si>
   <si>
     <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1177,22 +1219,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920061</v>
+        <v>22330051920105</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1200,22 +1242,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920212</v>
+        <v>22330051920157</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1223,39 +1265,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920121</v>
+        <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920070</v>
+        <v>22330051920212</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1264,29 +1306,144 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920317</v>
+        <v>22330051920039</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920145</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920070</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920317</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920126</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>CERON</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -143,6 +149,9 @@
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>GLORIA</t>
   </si>
   <si>
     <t>DANIELA</t>
@@ -1187,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1225,10 +1234,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1248,10 +1257,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1265,22 +1274,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920061</v>
+        <v>22330051920159</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1288,16 +1297,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1311,22 +1320,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920039</v>
+        <v>22330051920212</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1334,22 +1343,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920145</v>
+        <v>22330051920039</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1357,45 +1366,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920121</v>
+        <v>22330051920145</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920070</v>
+        <v>22330051920121</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1403,16 +1412,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920317</v>
+        <v>22330051920070</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1426,24 +1435,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920126</v>
+        <v>22330051920317</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920126</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>15</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -85,7 +85,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MENDOZA</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>CERON</t>
@@ -94,58 +97,46 @@
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
+    <t>CALOCA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
@@ -154,28 +145,16 @@
     <t>GLORIA</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>DANIELA</t>
   </si>
   <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ROSA</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
+    <t>ARLETH MARELY</t>
   </si>
 </sst>
 </file>
@@ -1021,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1047,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>93.02</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1073,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4">
-        <v>93.02</v>
+        <v>97.67</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1099,16 +1078,16 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>74.36</v>
+      </c>
+      <c r="H5">
         <v>7</v>
-      </c>
-      <c r="F5">
-        <v>32</v>
-      </c>
-      <c r="G5">
-        <v>82.05</v>
-      </c>
-      <c r="H5">
-        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1125,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1151,16 +1130,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>86.48999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1177,16 +1156,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8">
-        <v>78.56999999999999</v>
+        <v>76.19</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1228,22 +1207,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920105</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1251,7 +1230,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920157</v>
+        <v>22330051920321</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1260,13 +1239,13 @@
         <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1274,16 +1253,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920159</v>
+        <v>22330051920157</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1297,22 +1276,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920061</v>
+        <v>22330051920159</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1320,22 +1299,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920212</v>
+        <v>22330051920172</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1343,22 +1322,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920039</v>
+        <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1366,22 +1345,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920145</v>
+        <v>22330051920061</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1389,93 +1368,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920121</v>
+        <v>22330051920381</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920070</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920317</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920126</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>
